--- a/数据通路表、控制信号取值表_miniRV - 模板.xlsx
+++ b/数据通路表、控制信号取值表_miniRV - 模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CpuDesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5B54C7-743E-4DE7-A1A4-F2A29013E686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D23E17-22B7-46E7-B357-09AAF3F2206F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="20" windowWidth="25480" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="20" windowWidth="25480" windowHeight="15260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数据通路表(含控制信号)" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="167">
   <si>
     <t>所属单元</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -622,6 +622,74 @@
   </si>
   <si>
     <t>IN.inst[31:25|11:7]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mul</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mulh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>div</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>divu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slti</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sltu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sltiu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>or</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>andi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bltu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgeu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mulhu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -629,7 +697,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -688,6 +756,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -703,7 +779,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -798,21 +874,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -862,32 +946,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -905,6 +983,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -928,8 +1012,26 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -991,7 +1093,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1043,7 +1145,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1245,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:Q51"/>
+  <dimension ref="B2:Q60"/>
   <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.4609375" customWidth="1"/>
@@ -1267,737 +1369,737 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="37" t="s">
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="37" t="s">
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="39"/>
-      <c r="N3" s="23" t="s">
+      <c r="M3" s="38"/>
+      <c r="N3" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="35" t="s">
+      <c r="E4" s="39"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="8" t="s">
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="35" t="s">
+      <c r="L4" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="35" t="s">
+      <c r="M4" s="35"/>
+      <c r="N4" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="O4" s="36"/>
-      <c r="P4" s="35" t="s">
+      <c r="O4" s="35"/>
+      <c r="P4" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="Q4" s="36"/>
+      <c r="Q4" s="35"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="Q5" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="P6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="8" t="s">
+      <c r="P8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Q8" s="8" t="s">
+      <c r="Q8" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="E10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="8" t="s">
+      <c r="L10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="Q10" s="8" t="s">
+      <c r="Q10" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="M11" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="P11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="8" t="s">
+      <c r="P12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="F13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="M13" s="8" t="s">
+      <c r="M13" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="N13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="O13" s="8" t="s">
+      <c r="O13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="P13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Q13" s="8" t="s">
+      <c r="Q13" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="62" x14ac:dyDescent="0.35">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="M14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="O14" s="8" t="s">
+      <c r="O14" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="P14" s="8" t="s">
+      <c r="P14" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="Q14" s="8" t="s">
+      <c r="Q14" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="35" t="s">
+      <c r="C15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="35" t="s">
+      <c r="E15" s="39"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="8" t="s">
+      <c r="J15" s="35"/>
+      <c r="K15" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L15" s="35" t="s">
+      <c r="L15" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="35" t="s">
+      <c r="M15" s="35"/>
+      <c r="N15" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="O15" s="36"/>
-      <c r="P15" s="35" t="s">
+      <c r="O15" s="35"/>
+      <c r="P15" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="Q15" s="36"/>
+      <c r="Q15" s="35"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="C16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="8" t="s">
+      <c r="K16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="N16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="O16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="8" t="s">
+      <c r="P16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="Q16" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="31" t="s">
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="31" t="s">
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="M19" s="33"/>
-      <c r="N19" s="24" t="s">
+      <c r="M19" s="30"/>
+      <c r="N19" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="28" t="s">
+      <c r="E20" s="27"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="29"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="26"/>
       <c r="K20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L20" s="28" t="s">
+      <c r="L20" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="29"/>
-      <c r="N20" s="28" t="s">
+      <c r="M20" s="26"/>
+      <c r="N20" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="O20" s="29"/>
-      <c r="P20" s="28" t="s">
+      <c r="O20" s="26"/>
+      <c r="P20" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="Q20" s="29"/>
+      <c r="Q20" s="26"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -2056,10 +2158,10 @@
       <c r="D22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="E22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -2074,7 +2176,7 @@
       <c r="J22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L22" s="1" t="s">
@@ -2083,16 +2185,16 @@
       <c r="M22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P22" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q22" s="41" t="s">
+      <c r="N22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q22" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2106,10 +2208,10 @@
       <c r="D23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="7" t="s">
+      <c r="E23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -2124,7 +2226,7 @@
       <c r="J23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L23" s="1" t="s">
@@ -2133,16 +2235,16 @@
       <c r="M23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P23" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="41" t="s">
+      <c r="N23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q23" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2156,16 +2258,16 @@
       <c r="D24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7" t="s">
+      <c r="E24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2183,16 +2285,16 @@
       <c r="M24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P24" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q24" s="41" t="s">
+      <c r="N24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q24" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2206,10 +2308,10 @@
       <c r="D25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" s="7" t="s">
+      <c r="E25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2224,7 +2326,7 @@
       <c r="J25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="K25" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L25" s="1" t="s">
@@ -2233,16 +2335,16 @@
       <c r="M25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P25" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q25" s="41" t="s">
+      <c r="N25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q25" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2256,10 +2358,10 @@
       <c r="D26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="E26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -2274,7 +2376,7 @@
       <c r="J26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="K26" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L26" s="1" t="s">
@@ -2283,16 +2385,16 @@
       <c r="M26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P26" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q26" s="41" t="s">
+      <c r="N26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q26" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2306,16 +2408,16 @@
       <c r="D27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="7" t="s">
+      <c r="E27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2333,16 +2435,16 @@
       <c r="M27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P27" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q27" s="41" t="s">
+      <c r="N27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P27" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q27" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2356,10 +2458,10 @@
       <c r="D28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="E28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2374,7 +2476,7 @@
       <c r="J28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K28" s="7" t="s">
+      <c r="K28" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L28" s="1" t="s">
@@ -2383,16 +2485,16 @@
       <c r="M28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P28" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q28" s="41" t="s">
+      <c r="N28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q28" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2406,16 +2508,16 @@
       <c r="D29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" s="7" t="s">
+      <c r="E29" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2433,16 +2535,16 @@
       <c r="M29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N29" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P29" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q29" s="41" t="s">
+      <c r="N29" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q29" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2456,10 +2558,10 @@
       <c r="D30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="7" t="s">
+      <c r="E30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2474,7 +2576,7 @@
       <c r="J30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K30" s="7" t="s">
+      <c r="K30" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L30" s="1" t="s">
@@ -2483,16 +2585,16 @@
       <c r="M30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P30" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q30" s="41" t="s">
+      <c r="N30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P30" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q30" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2506,16 +2608,16 @@
       <c r="D31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="7" t="s">
+      <c r="E31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2533,16 +2635,16 @@
       <c r="M31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P31" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q31" s="41" t="s">
+      <c r="N31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q31" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2556,16 +2658,16 @@
       <c r="D32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" s="7" t="s">
+      <c r="E32" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -2586,13 +2688,13 @@
       <c r="N32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P32" s="18" t="s">
+      <c r="O32" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P32" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="Q32" s="18" t="s">
+      <c r="Q32" s="17" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2606,16 +2708,16 @@
       <c r="D33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="E33" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -2636,13 +2738,13 @@
       <c r="N33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O33" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P33" s="18" t="s">
+      <c r="O33" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P33" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="Q33" s="18" t="s">
+      <c r="Q33" s="17" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2656,16 +2758,16 @@
       <c r="D34" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" s="7" t="s">
+      <c r="E34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -2686,13 +2788,13 @@
       <c r="N34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P34" s="18" t="s">
+      <c r="O34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P34" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="Q34" s="18" t="s">
+      <c r="Q34" s="17" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2706,16 +2808,16 @@
       <c r="D35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F35" s="7" t="s">
+      <c r="E35" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -2736,13 +2838,13 @@
       <c r="N35" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P35" s="18" t="s">
+      <c r="O35" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P35" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="Q35" s="18" t="s">
+      <c r="Q35" s="17" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2756,10 +2858,10 @@
       <c r="D36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" s="7" t="s">
+      <c r="E36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -2768,10 +2870,10 @@
       <c r="H36" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J36" s="7" t="s">
+      <c r="I36" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>30</v>
       </c>
       <c r="K36" s="1" t="s">
@@ -2789,10 +2891,10 @@
       <c r="O36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P36" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q36" s="41" t="s">
+      <c r="P36" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q36" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2806,10 +2908,10 @@
       <c r="D37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="7" t="s">
+      <c r="E37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -2818,10 +2920,10 @@
       <c r="H37" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I37" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J37" s="7" t="s">
+      <c r="I37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" s="6" t="s">
         <v>30</v>
       </c>
       <c r="K37" s="1" t="s">
@@ -2839,10 +2941,10 @@
       <c r="O37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P37" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q37" s="41" t="s">
+      <c r="P37" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q37" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2856,10 +2958,10 @@
       <c r="D38" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="7" t="s">
+      <c r="E38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -2868,10 +2970,10 @@
       <c r="H38" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J38" s="7" t="s">
+      <c r="I38" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>30</v>
       </c>
       <c r="K38" s="1" t="s">
@@ -2889,10 +2991,10 @@
       <c r="O38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P38" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q38" s="41" t="s">
+      <c r="P38" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q38" s="18" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2906,16 +3008,16 @@
       <c r="D39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="7" t="s">
+      <c r="E39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -2933,190 +3035,933 @@
       <c r="M39" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P39" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q39" s="41" t="s">
+      <c r="N39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q39" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
+      <c r="B40" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q40" s="18" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="18"/>
-      <c r="Q41" s="18"/>
+      <c r="B41" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P41" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q41" s="18" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="18"/>
-      <c r="Q42" s="18"/>
+      <c r="B42" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q42" s="18" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
+      <c r="B43" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P43" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q43" s="18" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="18"/>
-      <c r="Q44" s="18"/>
+      <c r="B44" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P44" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q44" s="18" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
+      <c r="B45" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P45" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q45" s="18" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P46" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q46" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B47" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P47" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q47" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B48" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P48" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q48" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B49" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P49" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q49" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B50" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P50" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q50" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B51" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P51" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q51" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P52" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q52" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B53" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P53" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q53" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B54" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G54" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H54" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="I54" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="J54" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="L54" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M54" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N54" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O54" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="P54" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q54" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B55" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H55" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="I55" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="J55" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K55" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M55" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N55" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O55" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="P55" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q55" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B56" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F56" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G56" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H56" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="I56" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="J56" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K56" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="L56" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M56" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N56" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O56" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="P56" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q56" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B57" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F57" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H57" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="I57" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="J57" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="K57" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="L57" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="M57" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="N57" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O57" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="P57" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q57" s="24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B58" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="18"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B47" s="14" t="s">
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B59" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="18"/>
-      <c r="Q47" s="18"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B48" s="14" t="s">
+    </row>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B60" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="18"/>
-      <c r="Q48" s="18"/>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B51" s="3"/>
-      <c r="C51" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -3157,89 +4002,89 @@
   <sheetFormatPr defaultColWidth="11.07421875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.69140625" customWidth="1"/>
-    <col min="2" max="2" width="4.921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.23046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.69140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.23046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.3828125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.4609375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.23046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.61328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.23046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.3828125" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" style="4" customWidth="1"/>
-    <col min="15" max="15" width="9.69140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.23046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.69140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.23046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.3828125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.4609375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.23046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.61328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.23046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.3828125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.69140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
       <c r="M3"/>
       <c r="N3"/>
       <c r="O3"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B4" s="20"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="11" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>94</v>
       </c>
       <c r="M4"/>
@@ -3247,37 +4092,37 @@
       <c r="O4"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="10" t="s">
         <v>127</v>
       </c>
       <c r="M5"/>
@@ -3285,37 +4130,37 @@
       <c r="O5"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="10" t="s">
         <v>127</v>
       </c>
       <c r="M6"/>
@@ -3323,37 +4168,37 @@
       <c r="O6"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="10" t="s">
         <v>127</v>
       </c>
       <c r="M7"/>
@@ -3361,37 +4206,37 @@
       <c r="O7"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="10" t="s">
         <v>127</v>
       </c>
       <c r="M8"/>
@@ -3399,37 +4244,37 @@
       <c r="O8"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="10" t="s">
         <v>130</v>
       </c>
       <c r="M9"/>
@@ -3437,37 +4282,37 @@
       <c r="O9"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>0</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="11" t="s">
+      <c r="H10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="10" t="s">
         <v>45</v>
       </c>
       <c r="M10"/>
@@ -3475,37 +4320,37 @@
       <c r="O10"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>0</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="10" t="s">
         <v>127</v>
       </c>
       <c r="M11"/>
@@ -3513,37 +4358,37 @@
       <c r="O11"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>1</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="11" t="s">
+      <c r="J12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="10" t="s">
         <v>45</v>
       </c>
       <c r="M12"/>
@@ -3551,166 +4396,166 @@
       <c r="O12"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B16" s="25"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="4"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="5"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
